--- a/seed/sample_dp_sheet.xlsx
+++ b/seed/sample_dp_sheet.xlsx
@@ -628,8 +628,10 @@
           <t>VMS</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Candidate A</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -695,8 +697,10 @@
           <t>FTE</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Candidate C</t>
+        </is>
       </c>
       <c r="N5" s="1" t="n">
         <v>46310</v>
@@ -765,8 +769,10 @@
           <t>Sogeti</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Candidate D</t>
+        </is>
       </c>
       <c r="N6" s="1" t="n">
         <v>46310</v>
@@ -835,8 +841,10 @@
           <t>Sogeti</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Candidate E</t>
+        </is>
       </c>
       <c r="N7" s="1" t="n">
         <v>46273</v>
@@ -972,8 +980,10 @@
           <t>Sogeti</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Candidate B</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
